--- a/Results/Rise_Head/Normal/FindPrincipalComponents_PipelinePCA_Rise_Head/PCA_Dimension_Search_PipelinePCA.xlsx
+++ b/Results/Rise_Head/Normal/FindPrincipalComponents_PipelinePCA_Rise_Head/PCA_Dimension_Search_PipelinePCA.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -585,10 +585,40 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>Show Accuracy Threshold</t>
+        </is>
+      </c>
+      <c r="B15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Accuracy Threshold (%)</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Highlight Acceptable Accuracy</t>
+        </is>
+      </c>
+      <c r="B17" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>Master Path</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>/Users/mohammad/University/Bachelor Project/Final/Data/Rise_Head/Master Features/MASTER_Features_Rise_Head.xlsx</t>
         </is>
